--- a/healthcare_forms/004_physical_therapist_recommendation_form--healthcare_forms.xlsx
+++ b/healthcare_forms/004_physical_therapist_recommendation_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1026,8 +1026,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'dr._smith'}</t>
+          <t>dr._smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Dr. Smith'}</t>
+          <t>Dr. Smith</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'dr._johnson'}</t>
+          <t>dr._johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Dr. Johnson'}</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'dr._doe'}</t>
+          <t>dr._doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Dr. Doe'}</t>
+          <t>Dr. Doe</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'medicare'}</t>
+          <t>medicare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Medicare'}</t>
+          <t>Medicare</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'medicaid'}</t>
+          <t>medicaid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Medicaid'}</t>
+          <t>Medicaid</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'private_insurance'}</t>
+          <t>private_insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Private Insurance'}</t>
+          <t>Private Insurance</t>
         </is>
       </c>
     </row>
